--- a/forms/test-surveys/fd_test_census.xlsx
+++ b/forms/test-surveys/fd_test_census.xlsx
@@ -923,7 +923,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>regex(., 'HH-[0-9]{6}$')</t>
+          <t>regex(., '^HH-[0-9]{6}$')</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
